--- a/apps/supplier-web/public/templates/supplier-price-template.xlsx
+++ b/apps/supplier-web/public/templates/supplier-price-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" r:id="R915780a7cf6d4b1e"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как заполнить" sheetId="2" r:id="R6cfdeb4941844174"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" r:id="R2e423bff247c4564"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как заполнить" sheetId="2" r:id="Rbde6ee252d3c455c"/>
   </sheets>
 </workbook>
 </file>
@@ -14,54 +14,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="200" formatCode="@"/>
-    <numFmt numFmtId="201" formatCode="0.00"/>
-    <numFmt numFmtId="202" formatCode="General"/>
+    <numFmt numFmtId="201" formatCode="0"/>
+    <numFmt numFmtId="202" formatCode="0.00"/>
+    <numFmt numFmtId="203" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color rgb="FF006B59"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF006B59"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF4CE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -70,58 +40,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="201" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="202" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -326,7 +252,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="56" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="18" hidden="0" customWidth="1"/>
@@ -334,234 +260,86 @@
     <col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="37" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="8" t="str">
+    <row r="1">
+      <c r="A1" t="str">
         <v>Код</v>
       </c>
-      <c r="B1" s="8" t="str">
+      <c r="B1" t="str">
         <v>Название</v>
       </c>
-      <c r="C1" s="8" t="str">
+      <c r="C1" t="str">
         <v>Артикул</v>
       </c>
-      <c r="D1" s="8" t="str">
+      <c r="D1" t="str">
         <v>Штрихкод</v>
       </c>
-      <c r="E1" s="8" t="str">
+      <c r="E1" t="str">
         <v>Цена</v>
       </c>
-      <c r="F1" s="8" t="str">
+      <c r="F1" t="str">
         <v>Валюта</v>
       </c>
-      <c r="G1" s="8" t="str">
+      <c r="G1" t="str">
         <v>Остаток</v>
       </c>
-      <c r="H1" s="8" t="str">
+      <c r="H1" t="str">
         <v>Единица</v>
       </c>
-      <c r="I1" s="8" t="str">
+      <c r="I1" t="str">
         <v>Бренд</v>
       </c>
-      <c r="J1" s="8" t="str">
+      <c r="J1" t="str">
         <v>Производитель</v>
       </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13" t="str">
+      <c r="K1" t="str">
+        <v>Партия</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Срок годности</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="str">
         <v>EXAMPLE-001</v>
       </c>
-      <c r="B2" s="13" t="str">
-        <v>Пример: материал, тюбик 5 г</v>
-      </c>
-      <c r="C2" s="13" t="str">
+      <c r="B2" s="1" t="str">
+        <v>Пример: композит DemoDent A2, шприц 5 г</v>
+      </c>
+      <c r="C2" s="1" t="str">
         <v>MY-001</v>
       </c>
-      <c r="D2" s="13" t="str"/>
-      <c r="E2" s="14" t="n">
+      <c r="D2" s="2" t="str">
+        <v>2000000000015</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>1250.5</v>
       </c>
-      <c r="F2" s="15" t="str">
+      <c r="F2" t="str">
         <v>KZT</v>
       </c>
-      <c r="G2" s="16" t="n">
+      <c r="G2" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="H2" s="15" t="str">
+      <c r="H2" t="str">
         <v>шт.</v>
       </c>
-      <c r="I2" s="15" t="str"/>
-      <c r="J2" s="15" t="str"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
+      <c r="I2" t="str">
+        <v>DemoDent</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Demo Dental Manufacturing</v>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v>DEMO-2026-01</v>
+      </c>
+      <c r="L2" s="1" t="str">
+        <v>2030-12-31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -572,125 +350,141 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="94" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="37" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="100" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="5" t="str">
         <v>Шаблон прайса PlatformaMarket</v>
       </c>
-      <c r="B1" s="18" t="str"/>
+      <c r="B1" s="5" t="str"/>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="21" t="str">
+      <c r="A2" s="5" t="str">
         <v>Перед загрузкой</v>
       </c>
-      <c r="B2" s="18" t="str">
-        <v>Замените пример на листе «Товары» своими товарами. Одна строка — одна продаваемая упаковка.</v>
+      <c r="B2" s="5" t="str">
+        <v>Замените пример на листе «Товары» своими товарами. Все данные примера вымышлены, включая бренд, производителя и GTIN. Одна строка — одна продаваемая упаковка.</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="21" t="str">
+      <c r="A3" s="5" t="str">
         <v>Порядок работы</v>
       </c>
-      <c r="B3" s="18" t="str">
+      <c r="B3" s="5" t="str">
         <v>Сохраните XLSX, загрузите файл, сопоставьте столбцы и проверьте строки до подтверждения импорта.</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="21" t="str">
+      <c r="A4" s="5" t="str">
         <v>Код</v>
       </c>
-      <c r="B4" s="18" t="str">
+      <c r="B4" s="5" t="str">
         <v>Ваш постоянный код строки. Не меняйте его при обновлении того же товара из того же источника.</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="21" t="str">
+      <c r="A5" s="5" t="str">
         <v>Название</v>
       </c>
-      <c r="B5" s="18" t="str">
+      <c r="B5" s="5" t="str">
         <v>Полное название и упаковка, например тюбик 5 г. Обязательно для нового товара.</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="21" t="str">
+      <c r="A6" s="5" t="str">
         <v>Артикул</v>
       </c>
-      <c r="B6" s="18" t="str">
+      <c r="B6" s="5" t="str">
         <v>Код товара в вашей системе учёта. Храните как текст, чтобы сохранить начальные нули.</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="21" t="str">
+      <c r="A7" s="5" t="str">
         <v>Штрихкод</v>
       </c>
-      <c r="B7" s="18" t="str">
+      <c r="B7" s="5" t="str">
         <v>Цифры GTIN под штрихкодом на упаковке. Если его нет, оставьте пустым.</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="21" t="str">
+      <c r="A8" s="5" t="str">
         <v>Цена</v>
       </c>
-      <c r="B8" s="18" t="str">
+      <c r="B8" s="5" t="str">
         <v>Цена одной единицы продажи в тенге: 1250.50. При сопоставлении оставьте «Тенге», не «Тиыны».</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="21" t="str">
+      <c r="A9" s="5" t="str">
         <v>Валюта</v>
       </c>
-      <c r="B9" s="18" t="str">
+      <c r="B9" s="5" t="str">
         <v>KZT. Не пишите символ ₸ вместо кода валюты.</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="21" t="str">
+      <c r="A10" s="5" t="str">
         <v>Остаток</v>
       </c>
-      <c r="B10" s="18" t="str">
+      <c r="B10" s="5" t="str">
         <v>Количество в единицах продажи до вычета резервов площадки. 0 означает отсутствие товара.</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="21" t="str">
+      <c r="A11" s="5" t="str">
         <v>Единица</v>
       </c>
-      <c r="B11" s="18" t="str">
+      <c r="B11" s="5" t="str">
         <v>Единица продажи: шт., уп., кг и т. п. Название должно соответствовать фактической упаковке.</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="21" t="str">
+      <c r="A12" s="5" t="str">
         <v>Бренд и производитель</v>
       </c>
-      <c r="B12" s="18" t="str">
+      <c r="B12" s="5" t="str">
         <v>Укажите известные значения. Не подставляйте вымышленные названия вместо неизвестных.</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="21" t="str">
+      <c r="A13" s="5" t="str">
+        <v>Партия</v>
+      </c>
+      <c r="B13" s="5" t="str">
+        <v>Номер партии с упаковки. В примере DEMO-2026-01. Если неизвестен или неприменим, оставьте пустым.</v>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="5" t="str">
+        <v>Срок годности</v>
+      </c>
+      <c r="B14" s="5" t="str">
+        <v>Дата в формате ГГГГ-ММ-ДД, например 2030-12-31. Если неприменимо, оставьте пустым.</v>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="5" t="str">
         <v>Пустые значения</v>
       </c>
-      <c r="B13" s="18" t="str">
+      <c r="B15" s="5" t="str">
         <v>Не заменяйте неизвестные данные нулями. Ошибки обязательных полей будут показаны до подтверждения.</v>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="21" t="str">
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="5" t="str">
         <v>Обновление прайса</v>
       </c>
-      <c r="B14" s="18" t="str">
+      <c r="B16" s="5" t="str">
         <v>Выбирайте прежний источник и сохраняйте коды строк. Новые и неоднозначные товары требуют проверки.</v>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="21" t="str">
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="str">
         <v>Формат файла</v>
       </c>
-      <c r="B15" s="18" t="str">
+      <c r="B17" s="5" t="str">
         <v>Импортируется первый лист. До 5 000 строк и 20 МБ. Объединённые ячейки и итоги в таблице не нужны.</v>
       </c>
     </row>
